--- a/artfynd/A 9921-2023 artfynd.xlsx
+++ b/artfynd/A 9921-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY197"/>
+  <dimension ref="A1:AY200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22406,6 +22406,324 @@
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>104179900</v>
+      </c>
+      <c r="B198" t="n">
+        <v>85895</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Godkänd. Belägg granskat av validerare.</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>424</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Snögrinde skjutbana N, Gtl</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>695387</v>
+      </c>
+      <c r="R198" t="n">
+        <v>6362600</v>
+      </c>
+      <c r="S198" t="n">
+        <v>10</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AD198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT198" t="inlineStr"/>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>104179905</v>
+      </c>
+      <c r="B199" t="n">
+        <v>86486</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Godkänd. Belägg granskat av validerare.</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>510</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Snögrinde skjutbana N, Gtl</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>695315</v>
+      </c>
+      <c r="R199" t="n">
+        <v>6362568</v>
+      </c>
+      <c r="S199" t="n">
+        <v>10</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AD199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT199" t="inlineStr"/>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>104179903</v>
+      </c>
+      <c r="B200" t="n">
+        <v>85964</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Godkänd. Belägg granskat av validerare.</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Snögrinde skjutbana N, Gtl</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>695376</v>
+      </c>
+      <c r="R200" t="n">
+        <v>6362549</v>
+      </c>
+      <c r="S200" t="n">
+        <v>10</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AD200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT200" t="inlineStr"/>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9921-2023 artfynd.xlsx
+++ b/artfynd/A 9921-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9921-2023 artfynd.xlsx
+++ b/artfynd/A 9921-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY197"/>
+  <dimension ref="A1:AY196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8081,14 +8081,14 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>104142311</v>
+        <v>104130424</v>
       </c>
       <c r="B69" t="n">
-        <v>86139</v>
+        <v>89175</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8097,40 +8097,38 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>248956</v>
+        <v>2015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Snögrinde skjutbana, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>695396</v>
+        <v>695171.3293980963</v>
       </c>
       <c r="R69" t="n">
-        <v>6362509</v>
+        <v>6362799.676098357</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8157,48 +8155,53 @@
           <t>2022-10-16</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2022-10-16</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp, Cecilia Nygren, Laritza Pettersson, Niklas Johansson, Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
-        </is>
-      </c>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>104130424</v>
+        <v>104142525</v>
       </c>
       <c r="B70" t="n">
-        <v>89175</v>
+        <v>86139</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8207,38 +8210,40 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2015</v>
+        <v>248956</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Russpark, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>695171.3293980963</v>
+        <v>695310</v>
       </c>
       <c r="R70" t="n">
-        <v>6362799.676098357</v>
+        <v>6362557</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8265,76 +8270,71 @@
           <t>2022-10-16</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2022-10-16</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
+          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp, Cecilia Nygren, Brian Johnson, Niklas Johansson, Laritza Pettersson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>104142525</v>
+        <v>104142308</v>
       </c>
       <c r="B71" t="n">
-        <v>86139</v>
+        <v>90653</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>248956</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8343,14 +8343,14 @@
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Russpark, Gtl</t>
+          <t>Snögrinde skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>695310</v>
+        <v>695395.7551870565</v>
       </c>
       <c r="R71" t="n">
-        <v>6362557</v>
+        <v>6362508.985110709</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8380,9 +8380,19 @@
           <t>2022-10-16</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8403,7 +8413,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp, Cecilia Nygren, Brian Johnson, Niklas Johansson, Laritza Pettersson</t>
+          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp, Cecilia Nygren, Laritza Pettersson, Niklas Johansson, Brian Johnson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8414,10 +8424,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>104142308</v>
+        <v>104142527</v>
       </c>
       <c r="B72" t="n">
-        <v>90653</v>
+        <v>85241</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8430,21 +8440,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>3674</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8453,14 +8463,14 @@
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Snögrinde skjutbana, Gtl</t>
+          <t>Russpark, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>695395.7551870565</v>
+        <v>695309.066577228</v>
       </c>
       <c r="R72" t="n">
-        <v>6362508.985110709</v>
+        <v>6362556.159560451</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8523,7 +8533,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp, Cecilia Nygren, Laritza Pettersson, Niklas Johansson, Brian Johnson</t>
+          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp, Cecilia Nygren, Brian Johnson, Niklas Johansson, Laritza Pettersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8534,10 +8544,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>104142527</v>
+        <v>104129779</v>
       </c>
       <c r="B73" t="n">
-        <v>85241</v>
+        <v>85105</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8550,40 +8560,38 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Russpark, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>695309.066577228</v>
+        <v>695425.8626324137</v>
       </c>
       <c r="R73" t="n">
-        <v>6362556.159560451</v>
+        <v>6362558.500972861</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8612,7 +8620,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8622,7 +8630,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8631,33 +8639,28 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Martin Axegård, Helena Björnström, Majken Ekstrand, Mikael Jeppson, Michael Krikorev, Sofia Lund, Ossian Rydebjörk, kristina stenmarck, Birgitta Wasstorp, Cecilia Nygren, Brian Johnson, Niklas Johansson, Laritza Pettersson</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
-        </is>
-      </c>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>104129779</v>
+        <v>104129976</v>
       </c>
       <c r="B74" t="n">
-        <v>85105</v>
+        <v>85241</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8670,21 +8673,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8695,10 +8698,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>695425.8626324137</v>
+        <v>695410.6114486031</v>
       </c>
       <c r="R74" t="n">
-        <v>6362558.500972861</v>
+        <v>6362583.16031441</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8767,54 +8770,53 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>104129976</v>
+        <v>104179903</v>
       </c>
       <c r="B75" t="n">
-        <v>85241</v>
+        <v>86139</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3674</v>
+        <v>248956</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Snögrinde skjutbana N, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>695410.6114486031</v>
+        <v>695376</v>
       </c>
       <c r="R75" t="n">
-        <v>6362583.16031441</v>
+        <v>6362549</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8841,19 +8843,9 @@
           <t>2022-10-16</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>09:46</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8868,49 +8860,53 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>104179903</v>
+        <v>104179908</v>
       </c>
       <c r="B76" t="n">
-        <v>86139</v>
+        <v>85105</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>248956</v>
+        <v>3712</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8920,10 +8916,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>695376</v>
+        <v>695388.2641724584</v>
       </c>
       <c r="R76" t="n">
-        <v>6362549</v>
+        <v>6362597.757153463</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8953,9 +8949,19 @@
           <t>2022-10-16</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8986,37 +8992,37 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>104179908</v>
+        <v>104179904</v>
       </c>
       <c r="B77" t="n">
-        <v>85105</v>
+        <v>89815</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3712</v>
+        <v>3286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9026,10 +9032,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>695388.2641724584</v>
+        <v>695376</v>
       </c>
       <c r="R77" t="n">
-        <v>6362597.757153463</v>
+        <v>6362553</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9059,19 +9065,9 @@
           <t>2022-10-16</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9102,37 +9098,37 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>104179904</v>
+        <v>104179901</v>
       </c>
       <c r="B78" t="n">
-        <v>89815</v>
+        <v>85077</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3286</v>
+        <v>3762</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9142,10 +9138,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>695376</v>
+        <v>695331.9786657759</v>
       </c>
       <c r="R78" t="n">
-        <v>6362553</v>
+        <v>6362552.39279286</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9175,9 +9171,19 @@
           <t>2022-10-16</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9208,10 +9214,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>104179901</v>
+        <v>104179909</v>
       </c>
       <c r="B79" t="n">
-        <v>85077</v>
+        <v>85105</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9224,21 +9230,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9248,10 +9254,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>695331.9786657759</v>
+        <v>695375.2565411718</v>
       </c>
       <c r="R79" t="n">
-        <v>6362552.39279286</v>
+        <v>6362552.840649808</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9324,10 +9330,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>104179909</v>
+        <v>104179897</v>
       </c>
       <c r="B80" t="n">
-        <v>85105</v>
+        <v>90667</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9340,23 +9346,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3712</v>
+        <v>6047725</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9364,10 +9366,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>695375.2565411718</v>
+        <v>695389.1895964465</v>
       </c>
       <c r="R80" t="n">
-        <v>6362552.840649808</v>
+        <v>6362601.042450822</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9440,35 +9442,39 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>104179897</v>
+        <v>104179900</v>
       </c>
       <c r="B81" t="n">
-        <v>90667</v>
+        <v>86068</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6047725</v>
+        <v>424</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -9476,10 +9482,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>695389.1895964465</v>
+        <v>695386</v>
       </c>
       <c r="R81" t="n">
-        <v>6362601.042450822</v>
+        <v>6362600</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9509,19 +9515,9 @@
           <t>2022-10-16</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9552,10 +9548,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>104179900</v>
+        <v>104179902</v>
       </c>
       <c r="B82" t="n">
-        <v>86068</v>
+        <v>86139</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9568,21 +9564,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9592,10 +9588,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>695386</v>
+        <v>695376</v>
       </c>
       <c r="R82" t="n">
-        <v>6362600</v>
+        <v>6362579</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9658,37 +9654,37 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>104179902</v>
+        <v>104179907</v>
       </c>
       <c r="B83" t="n">
-        <v>86139</v>
+        <v>85105</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>248956</v>
+        <v>3712</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9698,10 +9694,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>695376</v>
+        <v>695363.8391033888</v>
       </c>
       <c r="R83" t="n">
-        <v>6362579</v>
+        <v>6362553.915472172</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9731,9 +9727,19 @@
           <t>2022-10-16</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9764,37 +9770,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>104179907</v>
+        <v>104179905</v>
       </c>
       <c r="B84" t="n">
-        <v>85105</v>
+        <v>86661</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3712</v>
+        <v>510</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9804,10 +9810,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>695363.8391033888</v>
+        <v>695315</v>
       </c>
       <c r="R84" t="n">
-        <v>6362553.915472172</v>
+        <v>6362568</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9837,19 +9843,9 @@
           <t>2022-10-16</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9880,37 +9876,37 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>104179905</v>
+        <v>104179898</v>
       </c>
       <c r="B85" t="n">
-        <v>86661</v>
+        <v>5135</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>510</v>
+        <v>105930</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9920,10 +9916,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>695315</v>
+        <v>695321.6395960141</v>
       </c>
       <c r="R85" t="n">
-        <v>6362568</v>
+        <v>6362576.206827682</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9953,9 +9949,19 @@
           <t>2022-10-16</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9986,50 +9992,50 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>104179898</v>
+        <v>104282753</v>
       </c>
       <c r="B86" t="n">
-        <v>5135</v>
+        <v>86068</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>105930</v>
+        <v>424</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Snögrinde skjutbana N, Gtl</t>
+          <t>Snögrinde skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>695321.6395960141</v>
+        <v>695458</v>
       </c>
       <c r="R86" t="n">
-        <v>6362576.206827682</v>
+        <v>6362642</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10059,19 +10065,9 @@
           <t>2022-10-16</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10086,12 +10082,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Michael Krikorev</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Michael Krikorev</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10102,14 +10098,14 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>104282753</v>
+        <v>104282746</v>
       </c>
       <c r="B87" t="n">
-        <v>86068</v>
+        <v>85200</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10118,21 +10114,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10142,10 +10138,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>695458</v>
+        <v>695372.0995569801</v>
       </c>
       <c r="R87" t="n">
-        <v>6362642</v>
+        <v>6362483.00562985</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10175,9 +10171,19 @@
           <t>2022-10-16</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10208,14 +10214,14 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>104282746</v>
+        <v>104282754</v>
       </c>
       <c r="B88" t="n">
-        <v>85200</v>
+        <v>86068</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10224,21 +10230,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10248,10 +10254,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>695372.0995569801</v>
+        <v>695421</v>
       </c>
       <c r="R88" t="n">
-        <v>6362483.00562985</v>
+        <v>6362562</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10281,19 +10287,9 @@
           <t>2022-10-16</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10324,10 +10320,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>104282754</v>
+        <v>104282744</v>
       </c>
       <c r="B89" t="n">
-        <v>86068</v>
+        <v>86139</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10340,21 +10336,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10364,10 +10360,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>695421</v>
+        <v>695446</v>
       </c>
       <c r="R89" t="n">
-        <v>6362562</v>
+        <v>6362631</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10430,37 +10426,37 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>104282744</v>
+        <v>104282731</v>
       </c>
       <c r="B90" t="n">
-        <v>86139</v>
+        <v>85105</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>248956</v>
+        <v>3712</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10470,10 +10466,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>695446</v>
+        <v>695441.9011917192</v>
       </c>
       <c r="R90" t="n">
-        <v>6362631</v>
+        <v>6362630.571319623</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10503,9 +10499,19 @@
           <t>2022-10-16</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10536,37 +10542,37 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>104282731</v>
+        <v>104282755</v>
       </c>
       <c r="B91" t="n">
-        <v>85105</v>
+        <v>86068</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10576,10 +10582,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>695441.9011917192</v>
+        <v>695397</v>
       </c>
       <c r="R91" t="n">
-        <v>6362630.571319623</v>
+        <v>6362550</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10609,19 +10615,9 @@
           <t>2022-10-16</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10652,37 +10648,37 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>104282755</v>
+        <v>104282734</v>
       </c>
       <c r="B92" t="n">
-        <v>86068</v>
+        <v>85244</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>424</v>
+        <v>6037417</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulfotad denisespindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>A.Ortega, Vila &amp; Fern.-Brime</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10692,10 +10688,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>695397</v>
+        <v>695369.8879692523</v>
       </c>
       <c r="R92" t="n">
-        <v>6362550</v>
+        <v>6362483.980306266</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10725,9 +10721,19 @@
           <t>2022-10-16</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10758,10 +10764,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>104282734</v>
+        <v>104282732</v>
       </c>
       <c r="B93" t="n">
-        <v>85244</v>
+        <v>85105</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10770,25 +10776,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6037417</v>
+        <v>3712</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gulfotad denisespindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>A.Ortega, Vila &amp; Fern.-Brime</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10798,10 +10804,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>695369.8879692523</v>
+        <v>695405.4733152154</v>
       </c>
       <c r="R93" t="n">
-        <v>6362483.980306266</v>
+        <v>6362532.137537695</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10874,10 +10880,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>104282732</v>
+        <v>104282722</v>
       </c>
       <c r="B94" t="n">
-        <v>85105</v>
+        <v>85278</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10886,25 +10892,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10914,10 +10920,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>695405.4733152154</v>
+        <v>695368.8079360173</v>
       </c>
       <c r="R94" t="n">
-        <v>6362532.137537695</v>
+        <v>6362483.92868471</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10990,10 +10996,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>104282722</v>
+        <v>104282764</v>
       </c>
       <c r="B95" t="n">
-        <v>85278</v>
+        <v>85241</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11002,25 +11008,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11030,10 +11036,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>695368.8079360173</v>
+        <v>695374.6193137621</v>
       </c>
       <c r="R95" t="n">
-        <v>6362483.92868471</v>
+        <v>6362486.907406477</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11106,10 +11112,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>104282764</v>
+        <v>109534717</v>
       </c>
       <c r="B96" t="n">
-        <v>85241</v>
+        <v>8377</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11122,37 +11128,38 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3674</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Snögrinde skjutbana, Gtl</t>
+          <t>Utskogen, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>695374.6193137621</v>
+        <v>695164.2131710016</v>
       </c>
       <c r="R96" t="n">
-        <v>6362486.907406477</v>
+        <v>6362631.347146432</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11176,7 +11183,7 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2022-10-16</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
@@ -11186,12 +11193,17 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2022-10-16</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11206,26 +11218,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>109534717</v>
+        <v>109534776</v>
       </c>
       <c r="B97" t="n">
-        <v>8377</v>
+        <v>98520</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11238,21 +11246,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>222498</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11263,10 +11271,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>695164.2131710016</v>
+        <v>695345.5534262478</v>
       </c>
       <c r="R97" t="n">
-        <v>6362631.347146432</v>
+        <v>6362585.452321053</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11311,11 +11319,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -11328,19 +11331,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Martin Andersson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Martin Andersson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>109534776</v>
+        <v>109534927</v>
       </c>
       <c r="B98" t="n">
         <v>98520</v>
@@ -11381,10 +11384,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>695345.5534262478</v>
+        <v>695284.4873564986</v>
       </c>
       <c r="R98" t="n">
-        <v>6362585.452321053</v>
+        <v>6362492.863913513</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11441,22 +11444,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Martin Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Martin Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>109534927</v>
+        <v>109534436</v>
       </c>
       <c r="B99" t="n">
-        <v>98520</v>
+        <v>96355</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11469,21 +11472,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11494,10 +11497,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>695284.4873564986</v>
+        <v>695304.2170176189</v>
       </c>
       <c r="R99" t="n">
-        <v>6362492.863913513</v>
+        <v>6362770.914268165</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11554,22 +11557,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Martin Andersson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Martin Andersson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>109534436</v>
+        <v>109534905</v>
       </c>
       <c r="B100" t="n">
-        <v>96355</v>
+        <v>56411</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11578,25 +11581,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219862</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11607,10 +11610,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>695304.2170176189</v>
+        <v>695391.3320269433</v>
       </c>
       <c r="R100" t="n">
-        <v>6362770.914268165</v>
+        <v>6362510.934425471</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11679,10 +11682,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>109534905</v>
+        <v>109534766</v>
       </c>
       <c r="B101" t="n">
-        <v>56411</v>
+        <v>99398</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11691,25 +11694,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11720,10 +11723,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>695391.3320269433</v>
+        <v>695345.5534262478</v>
       </c>
       <c r="R101" t="n">
-        <v>6362510.934425471</v>
+        <v>6362585.452321053</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11792,10 +11795,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>109534766</v>
+        <v>109534773</v>
       </c>
       <c r="B102" t="n">
-        <v>99398</v>
+        <v>96361</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11808,21 +11811,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221235</v>
+        <v>219864</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11905,7 +11908,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>109534773</v>
+        <v>109534913</v>
       </c>
       <c r="B103" t="n">
         <v>96361</v>
@@ -11946,10 +11949,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>695345.5534262478</v>
+        <v>695284.4873564986</v>
       </c>
       <c r="R103" t="n">
-        <v>6362585.452321053</v>
+        <v>6362492.863913513</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12006,66 +12009,65 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Martin Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Martin Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>109534913</v>
+        <v>112729807</v>
       </c>
       <c r="B104" t="n">
-        <v>96361</v>
+        <v>86215</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>219864</v>
+        <v>6003295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Utskogen, Gtl</t>
+          <t>Klinte skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>695284.4873564986</v>
+        <v>695414</v>
       </c>
       <c r="R104" t="n">
-        <v>6362492.863913513</v>
+        <v>6362683</v>
       </c>
       <c r="S104" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12089,22 +12091,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-14</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12119,19 +12111,23 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr"/>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>112729807</v>
+        <v>112730611</v>
       </c>
       <c r="B105" t="n">
         <v>86215</v>
@@ -12167,14 +12163,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Klinte skjutbana, Gtl</t>
+          <t>Skjutbanan, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>695414</v>
+        <v>695393</v>
       </c>
       <c r="R105" t="n">
-        <v>6362683</v>
+        <v>6362602</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12221,12 +12217,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -12237,53 +12233,56 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>112730611</v>
+        <v>112723847</v>
       </c>
       <c r="B106" t="n">
-        <v>86215</v>
+        <v>85722</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Skjutbanan, Gtl</t>
+          <t>Snögrinde skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>695393</v>
+        <v>695211</v>
       </c>
       <c r="R106" t="n">
-        <v>6362602</v>
+        <v>6362578</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12321,18 +12320,19 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, kristina stenmarck, Majken Ekstrand, Gillis Aronsson, Linnea Ingelsbo, Sten Svantesson, Michael Krikorev, Helena Björnström</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -12343,7 +12343,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>112723847</v>
+        <v>112729817</v>
       </c>
       <c r="B107" t="n">
         <v>85722</v>
@@ -12377,22 +12377,19 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Snögrinde skjutbana, Gtl</t>
+          <t>Klinte skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>695211</v>
+        <v>695441</v>
       </c>
       <c r="R107" t="n">
-        <v>6362578</v>
+        <v>6362698</v>
       </c>
       <c r="S107" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12430,19 +12427,18 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, kristina stenmarck, Majken Ekstrand, Gillis Aronsson, Linnea Ingelsbo, Sten Svantesson, Michael Krikorev, Helena Björnström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -12453,10 +12449,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>112729817</v>
+        <v>112729697</v>
       </c>
       <c r="B108" t="n">
-        <v>85722</v>
+        <v>85586</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12469,21 +12465,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12493,10 +12489,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>695441</v>
+        <v>695358</v>
       </c>
       <c r="R108" t="n">
-        <v>6362698</v>
+        <v>6362670</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12543,12 +12539,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Alexander Singer, Helena Björnström, Mikael Jeppson, Laritza Pettersson, Erland Lindblad, Thomas Jeppesen</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -12559,10 +12555,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>112729697</v>
+        <v>112723784</v>
       </c>
       <c r="B109" t="n">
-        <v>85586</v>
+        <v>85722</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12575,37 +12571,40 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Klinte skjutbana, Gtl</t>
+          <t>Snögrinde skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>695358</v>
+        <v>695291</v>
       </c>
       <c r="R109" t="n">
-        <v>6362670</v>
+        <v>6362524</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12643,18 +12642,19 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Alexander Singer, Helena Björnström, Mikael Jeppson, Laritza Pettersson, Erland Lindblad, Thomas Jeppesen</t>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, kristina stenmarck, Majken Ekstrand, Gillis Aronsson, Linnea Ingelsbo, Sten Svantesson, Michael Krikorev, Helena Björnström</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -12665,10 +12665,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>112723784</v>
+        <v>112730608</v>
       </c>
       <c r="B110" t="n">
-        <v>85722</v>
+        <v>85586</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12681,40 +12681,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Snögrinde skjutbana, Gtl</t>
+          <t>Skjutbanan, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>695291</v>
+        <v>695384</v>
       </c>
       <c r="R110" t="n">
-        <v>6362524</v>
+        <v>6362576</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12752,19 +12749,18 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, kristina stenmarck, Majken Ekstrand, Gillis Aronsson, Linnea Ingelsbo, Sten Svantesson, Michael Krikorev, Helena Björnström</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -12775,10 +12771,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>112730608</v>
+        <v>112725263</v>
       </c>
       <c r="B111" t="n">
-        <v>85586</v>
+        <v>85705</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12787,38 +12783,41 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3712</v>
+        <v>248955</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Skjutbanan, Gtl</t>
+          <t>Klinte skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>695384</v>
+        <v>695444</v>
       </c>
       <c r="R111" t="n">
-        <v>6362576</v>
+        <v>6362670</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12859,18 +12858,19 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Petra Wikström, Anna Helmersson, Niklas Johansson, Brian Johnson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12881,14 +12881,14 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>112725263</v>
+        <v>112730605</v>
       </c>
       <c r="B112" t="n">
-        <v>85705</v>
+        <v>86252</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -12897,37 +12897,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>248955</v>
+        <v>3767</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Klinte skjutbana, Gtl</t>
+          <t>Skjutbanan, Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>695444</v>
+        <v>695280</v>
       </c>
       <c r="R112" t="n">
-        <v>6362670</v>
+        <v>6362612</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12968,19 +12965,18 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Niklas Johansson, Brian Johnson</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12991,50 +12987,50 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>112730605</v>
+        <v>112729698</v>
       </c>
       <c r="B113" t="n">
-        <v>86252</v>
+        <v>85722</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Skjutbanan, Gtl</t>
+          <t>Klinte skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>695280</v>
+        <v>695315</v>
       </c>
       <c r="R113" t="n">
-        <v>6362612</v>
+        <v>6362690</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13081,12 +13077,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Alexander Singer, Helena Björnström, Mikael Jeppson, Laritza Pettersson, Erland Lindblad, Thomas Jeppesen</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -13097,10 +13093,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>112729698</v>
+        <v>112729806</v>
       </c>
       <c r="B114" t="n">
-        <v>85722</v>
+        <v>85586</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13113,21 +13109,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13137,10 +13133,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>695315</v>
+        <v>695447</v>
       </c>
       <c r="R114" t="n">
-        <v>6362690</v>
+        <v>6362662</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13187,12 +13183,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Alexander Singer, Helena Björnström, Mikael Jeppson, Laritza Pettersson, Erland Lindblad, Thomas Jeppesen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -13203,50 +13199,53 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>112729806</v>
+        <v>112725262</v>
       </c>
       <c r="B115" t="n">
-        <v>85586</v>
+        <v>86215</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Klinte skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>695447</v>
+        <v>695441</v>
       </c>
       <c r="R115" t="n">
-        <v>6362662</v>
+        <v>6362682</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13287,18 +13286,19 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström, Anna Helmersson, Niklas Johansson, Brian Johnson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -13309,10 +13309,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>112725262</v>
+        <v>112729812</v>
       </c>
       <c r="B116" t="n">
-        <v>86215</v>
+        <v>89815</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13325,37 +13325,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6003295</v>
+        <v>3286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Klinte skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>695441</v>
+        <v>695440</v>
       </c>
       <c r="R116" t="n">
-        <v>6362682</v>
+        <v>6362671</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13396,19 +13393,18 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Niklas Johansson, Brian Johnson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -13419,50 +13415,50 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>112729812</v>
+        <v>112729832</v>
       </c>
       <c r="B117" t="n">
-        <v>89815</v>
+        <v>85722</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3286</v>
+        <v>3674</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Klinte skjutbana, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>695440</v>
+        <v>695274</v>
       </c>
       <c r="R117" t="n">
-        <v>6362671</v>
+        <v>6362513</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13509,12 +13505,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -13525,7 +13521,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>112729832</v>
+        <v>112725267</v>
       </c>
       <c r="B118" t="n">
         <v>85722</v>
@@ -13559,16 +13555,19 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Klinte skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>695274</v>
+        <v>695369</v>
       </c>
       <c r="R118" t="n">
-        <v>6362513</v>
+        <v>6362506</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13609,18 +13608,19 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Petra Wikström, Anna Helmersson, Niklas Johansson, Brian Johnson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -13631,7 +13631,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>112725267</v>
+        <v>112723769</v>
       </c>
       <c r="B119" t="n">
         <v>85722</v>
@@ -13670,17 +13670,17 @@
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Klinte skjutbana, Gtl</t>
+          <t>Snögrinde skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>695369</v>
+        <v>695332</v>
       </c>
       <c r="R119" t="n">
-        <v>6362506</v>
+        <v>6362528</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13725,12 +13725,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Niklas Johansson, Brian Johnson</t>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, kristina stenmarck, Majken Ekstrand, Gillis Aronsson, Linnea Ingelsbo, Sten Svantesson, Michael Krikorev, Helena Björnström</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -13741,32 +13741,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>112723769</v>
+        <v>112730615</v>
       </c>
       <c r="B120" t="n">
-        <v>85722</v>
+        <v>86133</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -13775,22 +13775,19 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Snögrinde skjutbana, Gtl</t>
+          <t>Skjutbanan, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>695332</v>
+        <v>695364</v>
       </c>
       <c r="R120" t="n">
-        <v>6362528</v>
+        <v>6362717</v>
       </c>
       <c r="S120" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13828,19 +13825,18 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, kristina stenmarck, Majken Ekstrand, Gillis Aronsson, Linnea Ingelsbo, Sten Svantesson, Michael Krikorev, Helena Björnström</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -13851,50 +13847,50 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>112730615</v>
+        <v>112729826</v>
       </c>
       <c r="B121" t="n">
-        <v>86133</v>
+        <v>85759</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Skjutbanan, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>695364</v>
+        <v>695305</v>
       </c>
       <c r="R121" t="n">
-        <v>6362717</v>
+        <v>6362511</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13941,12 +13937,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -13957,7 +13953,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>112729826</v>
+        <v>112730609</v>
       </c>
       <c r="B122" t="n">
         <v>85759</v>
@@ -13993,14 +13989,14 @@
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Skjutbanan, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>695305</v>
+        <v>695360</v>
       </c>
       <c r="R122" t="n">
-        <v>6362511</v>
+        <v>6362790</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14047,12 +14043,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -14063,10 +14059,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>112730609</v>
+        <v>112723941</v>
       </c>
       <c r="B123" t="n">
-        <v>85759</v>
+        <v>85722</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14075,41 +14071,44 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Skjutbanan, Gtl</t>
+          <t>Snögrinde skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>695360</v>
+        <v>695252</v>
       </c>
       <c r="R123" t="n">
-        <v>6362790</v>
+        <v>6362818</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14147,18 +14146,19 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, kristina stenmarck, Majken Ekstrand, Gillis Aronsson, Linnea Ingelsbo, Sten Svantesson, Michael Krikorev, Helena Björnström</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -14169,10 +14169,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>112723941</v>
+        <v>112716773</v>
       </c>
       <c r="B124" t="n">
-        <v>85722</v>
+        <v>85586</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14185,37 +14185,35 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Snögrinde skjutbana, Gtl</t>
+          <t>Utskogen, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>695252</v>
+        <v>695320</v>
       </c>
       <c r="R124" t="n">
-        <v>6362818</v>
+        <v>6362625</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -14256,30 +14254,25 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, kristina stenmarck, Majken Ekstrand, Gillis Aronsson, Linnea Ingelsbo, Sten Svantesson, Michael Krikorev, Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, Gotland</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>112716773</v>
+        <v>112723931</v>
       </c>
       <c r="B125" t="n">
         <v>85586</v>
@@ -14313,17 +14306,19 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Utskogen, Gtl</t>
+          <t>Snögrinde skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>695320</v>
+        <v>695240</v>
       </c>
       <c r="R125" t="n">
-        <v>6362625</v>
+        <v>6362861</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -14364,28 +14359,33 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY125" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, kristina stenmarck, Majken Ekstrand, Gillis Aronsson, Linnea Ingelsbo, Sten Svantesson, Michael Krikorev, Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>112723931</v>
+        <v>112723909</v>
       </c>
       <c r="B126" t="n">
-        <v>85586</v>
+        <v>85722</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14398,21 +14398,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14425,10 +14425,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>695240</v>
+        <v>695158</v>
       </c>
       <c r="R126" t="n">
-        <v>6362861</v>
+        <v>6362880</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14492,7 +14492,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>112723909</v>
+        <v>112730614</v>
       </c>
       <c r="B127" t="n">
         <v>85722</v>
@@ -14526,22 +14526,19 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Snögrinde skjutbana, Gtl</t>
+          <t>Skjutbanan, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>695158</v>
+        <v>695397</v>
       </c>
       <c r="R127" t="n">
-        <v>6362880</v>
+        <v>6362609</v>
       </c>
       <c r="S127" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14579,19 +14576,18 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, kristina stenmarck, Majken Ekstrand, Gillis Aronsson, Linnea Ingelsbo, Sten Svantesson, Michael Krikorev, Helena Björnström</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -14602,7 +14598,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>112730614</v>
+        <v>112725265</v>
       </c>
       <c r="B128" t="n">
         <v>85722</v>
@@ -14636,16 +14632,19 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Skjutbanan, Gtl</t>
+          <t>Klinte skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>695397</v>
+        <v>695436</v>
       </c>
       <c r="R128" t="n">
-        <v>6362609</v>
+        <v>6362691</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14686,18 +14685,19 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Petra Wikström, Anna Helmersson, Niklas Johansson, Brian Johnson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -14708,10 +14708,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>112725265</v>
+        <v>112729828</v>
       </c>
       <c r="B129" t="n">
-        <v>85722</v>
+        <v>89351</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14724,37 +14724,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3674</v>
+        <v>4188</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Klinte skjutbana, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>695436</v>
+        <v>695267</v>
       </c>
       <c r="R129" t="n">
-        <v>6362691</v>
+        <v>6362472</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14795,19 +14792,18 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Niklas Johansson, Brian Johnson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -14818,10 +14814,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>112729828</v>
+        <v>112729700</v>
       </c>
       <c r="B130" t="n">
-        <v>89351</v>
+        <v>85722</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14834,34 +14830,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4188</v>
+        <v>3674</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Klinte skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>695267</v>
+        <v>695367</v>
       </c>
       <c r="R130" t="n">
-        <v>6362472</v>
+        <v>6362520</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14908,12 +14904,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Alexander Singer, Helena Björnström, Mikael Jeppson, Laritza Pettersson, Erland Lindblad, Thomas Jeppesen</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -14924,7 +14920,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>112729700</v>
+        <v>112729699</v>
       </c>
       <c r="B131" t="n">
         <v>85722</v>
@@ -14964,10 +14960,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>695367</v>
+        <v>695336</v>
       </c>
       <c r="R131" t="n">
-        <v>6362520</v>
+        <v>6362691</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15030,37 +15026,37 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>112729699</v>
+        <v>112729691</v>
       </c>
       <c r="B132" t="n">
-        <v>85722</v>
+        <v>86215</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15070,10 +15066,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>695336</v>
+        <v>695287</v>
       </c>
       <c r="R132" t="n">
-        <v>6362691</v>
+        <v>6362607</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15136,7 +15132,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>112729691</v>
+        <v>112725260</v>
       </c>
       <c r="B133" t="n">
         <v>86215</v>
@@ -15170,16 +15166,19 @@
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Klinte skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>695287</v>
+        <v>695439</v>
       </c>
       <c r="R133" t="n">
-        <v>6362607</v>
+        <v>6362700</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15220,18 +15219,19 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Alexander Singer, Helena Björnström, Mikael Jeppson, Laritza Pettersson, Erland Lindblad, Thomas Jeppesen</t>
+          <t>Petra Wikström, Anna Helmersson, Niklas Johansson, Brian Johnson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -15242,53 +15242,50 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>112725260</v>
+        <v>112729814</v>
       </c>
       <c r="B134" t="n">
-        <v>86215</v>
+        <v>85722</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Klinte skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>695439</v>
+        <v>695390</v>
       </c>
       <c r="R134" t="n">
-        <v>6362700</v>
+        <v>6362690</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15329,19 +15326,18 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Niklas Johansson, Brian Johnson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -15352,7 +15348,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>112729814</v>
+        <v>112723839</v>
       </c>
       <c r="B135" t="n">
         <v>85722</v>
@@ -15386,19 +15382,22 @@
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Klinte skjutbana, Gtl</t>
+          <t>Snögrinde skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>695390</v>
+        <v>695239</v>
       </c>
       <c r="R135" t="n">
-        <v>6362690</v>
+        <v>6362500</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15436,18 +15435,19 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, kristina stenmarck, Majken Ekstrand, Gillis Aronsson, Linnea Ingelsbo, Sten Svantesson, Michael Krikorev, Helena Björnström</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -15458,56 +15458,53 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>112723839</v>
+        <v>112730610</v>
       </c>
       <c r="B136" t="n">
-        <v>85722</v>
+        <v>86215</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Snögrinde skjutbana, Gtl</t>
+          <t>Skjutbanan, Gtl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>695239</v>
+        <v>695397</v>
       </c>
       <c r="R136" t="n">
-        <v>6362500</v>
+        <v>6362609</v>
       </c>
       <c r="S136" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15545,19 +15542,18 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, kristina stenmarck, Majken Ekstrand, Gillis Aronsson, Linnea Ingelsbo, Sten Svantesson, Michael Krikorev, Helena Björnström</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -15568,50 +15564,53 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>112730610</v>
+        <v>112725259</v>
       </c>
       <c r="B137" t="n">
-        <v>86215</v>
+        <v>85586</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Skjutbanan, Gtl</t>
+          <t>Klinte skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>695397</v>
+        <v>695403</v>
       </c>
       <c r="R137" t="n">
-        <v>6362609</v>
+        <v>6362729</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15652,18 +15651,19 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Petra Wikström, Anna Helmersson, Niklas Johansson, Brian Johnson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -15674,10 +15674,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>112725259</v>
+        <v>112729831</v>
       </c>
       <c r="B138" t="n">
-        <v>85586</v>
+        <v>85722</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15690,37 +15690,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Klinte skjutbana, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>695403</v>
+        <v>695253</v>
       </c>
       <c r="R138" t="n">
-        <v>6362729</v>
+        <v>6362489</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15761,19 +15758,18 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Petra Wikström, Anna Helmersson, Niklas Johansson, Brian Johnson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -15784,7 +15780,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>112729831</v>
+        <v>112723853</v>
       </c>
       <c r="B139" t="n">
         <v>85722</v>
@@ -15818,19 +15814,22 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Snögrinde skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>695253</v>
+        <v>695191</v>
       </c>
       <c r="R139" t="n">
-        <v>6362489</v>
+        <v>6362593</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15868,18 +15867,19 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, kristina stenmarck, Majken Ekstrand, Gillis Aronsson, Linnea Ingelsbo, Sten Svantesson, Michael Krikorev, Helena Björnström</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -15890,56 +15890,53 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>112723853</v>
+        <v>112729692</v>
       </c>
       <c r="B140" t="n">
-        <v>85722</v>
+        <v>86215</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Snögrinde skjutbana, Gtl</t>
+          <t>Klinte skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>695191</v>
+        <v>695339</v>
       </c>
       <c r="R140" t="n">
-        <v>6362593</v>
+        <v>6362677</v>
       </c>
       <c r="S140" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15977,19 +15974,18 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, kristina stenmarck, Majken Ekstrand, Gillis Aronsson, Linnea Ingelsbo, Sten Svantesson, Michael Krikorev, Helena Björnström</t>
+          <t>Alexander Singer, Helena Björnström, Mikael Jeppson, Laritza Pettersson, Erland Lindblad, Thomas Jeppesen</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -16000,50 +15996,50 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>112729692</v>
+        <v>112730613</v>
       </c>
       <c r="B141" t="n">
-        <v>86215</v>
+        <v>85722</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Klinte skjutbana, Gtl</t>
+          <t>Skjutbanan, Gtl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>695339</v>
+        <v>695368</v>
       </c>
       <c r="R141" t="n">
-        <v>6362677</v>
+        <v>6362722</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16090,12 +16086,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Alexander Singer, Helena Björnström, Mikael Jeppson, Laritza Pettersson, Erland Lindblad, Thomas Jeppesen</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -16106,10 +16102,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>112730613</v>
+        <v>112729825</v>
       </c>
       <c r="B142" t="n">
-        <v>85722</v>
+        <v>91175</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16122,34 +16118,30 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3674</v>
+        <v>6047725</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Skjutbanan, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>695368</v>
+        <v>695278</v>
       </c>
       <c r="R142" t="n">
-        <v>6362722</v>
+        <v>6362519</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16196,12 +16188,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -16212,10 +16204,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>112729825</v>
+        <v>112730612</v>
       </c>
       <c r="B143" t="n">
-        <v>91175</v>
+        <v>85722</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16228,30 +16220,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6047725</v>
+        <v>3674</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Skjutbanan, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>695278</v>
+        <v>695360</v>
       </c>
       <c r="R143" t="n">
-        <v>6362519</v>
+        <v>6362790</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16298,12 +16294,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -16314,7 +16310,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>112730612</v>
+        <v>112729830</v>
       </c>
       <c r="B144" t="n">
         <v>85722</v>
@@ -16350,14 +16346,14 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Skjutbanan, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>695360</v>
+        <v>695256</v>
       </c>
       <c r="R144" t="n">
-        <v>6362790</v>
+        <v>6362479</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16404,12 +16400,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -16420,10 +16416,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>112729830</v>
+        <v>112730606</v>
       </c>
       <c r="B145" t="n">
-        <v>85722</v>
+        <v>85586</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16436,34 +16432,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Skjutbanan, Gtl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>695256</v>
+        <v>695360</v>
       </c>
       <c r="R145" t="n">
-        <v>6362479</v>
+        <v>6362790</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16510,12 +16506,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -16526,10 +16522,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>112730606</v>
+        <v>112716645</v>
       </c>
       <c r="B146" t="n">
-        <v>85586</v>
+        <v>85722</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16542,37 +16538,38 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Skjutbanan, Gtl</t>
+          <t>Utskogen, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>695360</v>
+        <v>695354</v>
       </c>
       <c r="R146" t="n">
-        <v>6362790</v>
+        <v>6362524</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -16616,23 +16613,19 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
-        </is>
-      </c>
-      <c r="AY146" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, Gotland</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>112716645</v>
+        <v>112729816</v>
       </c>
       <c r="B147" t="n">
         <v>85722</v>
@@ -16666,20 +16659,19 @@
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Utskogen, Gtl</t>
+          <t>Klinte skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>695354</v>
+        <v>695419</v>
       </c>
       <c r="R147" t="n">
-        <v>6362524</v>
+        <v>6362685</v>
       </c>
       <c r="S147" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16723,19 +16715,23 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY147" t="inlineStr"/>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>112729816</v>
+        <v>112716812</v>
       </c>
       <c r="B148" t="n">
         <v>85722</v>
@@ -16769,19 +16765,22 @@
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Klinte skjutbana, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>695419</v>
+        <v>695314</v>
       </c>
       <c r="R148" t="n">
-        <v>6362685</v>
+        <v>6362657</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16819,18 +16818,19 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -16841,10 +16841,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>112716812</v>
+        <v>112730607</v>
       </c>
       <c r="B149" t="n">
-        <v>85722</v>
+        <v>85586</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16857,40 +16857,37 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Skjutbanan, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>695314</v>
+        <v>695397</v>
       </c>
       <c r="R149" t="n">
-        <v>6362657</v>
+        <v>6362609</v>
       </c>
       <c r="S149" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16928,19 +16925,18 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -16951,50 +16947,50 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>112730607</v>
+        <v>112729810</v>
       </c>
       <c r="B150" t="n">
-        <v>85586</v>
+        <v>86215</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Skjutbanan, Gtl</t>
+          <t>Klinte skjutbana, Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>695397</v>
+        <v>695428</v>
       </c>
       <c r="R150" t="n">
-        <v>6362609</v>
+        <v>6362692</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17041,12 +17037,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -17057,7 +17053,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>112729810</v>
+        <v>112729693</v>
       </c>
       <c r="B151" t="n">
         <v>86215</v>
@@ -17097,10 +17093,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>695428</v>
+        <v>695387</v>
       </c>
       <c r="R151" t="n">
-        <v>6362692</v>
+        <v>6362626</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17147,12 +17143,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Alexander Singer, Helena Björnström, Mikael Jeppson, Laritza Pettersson, Erland Lindblad, Thomas Jeppesen</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -17163,14 +17159,14 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>112729693</v>
+        <v>112772290</v>
       </c>
       <c r="B152" t="n">
-        <v>86215</v>
+        <v>85760</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -17203,10 +17199,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>695387</v>
+        <v>695265</v>
       </c>
       <c r="R152" t="n">
-        <v>6362626</v>
+        <v>6362624</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17253,12 +17249,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Alexander Singer, Helena Björnström, Mikael Jeppson, Laritza Pettersson, Erland Lindblad, Thomas Jeppesen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -17269,10 +17265,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>112772290</v>
+        <v>112772349</v>
       </c>
       <c r="B153" t="n">
-        <v>85760</v>
+        <v>85723</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17281,25 +17277,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17309,10 +17305,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>695265</v>
+        <v>695301</v>
       </c>
       <c r="R153" t="n">
-        <v>6362624</v>
+        <v>6362745</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17375,7 +17371,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>112772349</v>
+        <v>112772348</v>
       </c>
       <c r="B154" t="n">
         <v>85723</v>
@@ -17415,10 +17411,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>695301</v>
+        <v>695341</v>
       </c>
       <c r="R154" t="n">
-        <v>6362745</v>
+        <v>6362752</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17481,7 +17477,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>112772348</v>
+        <v>112772355</v>
       </c>
       <c r="B155" t="n">
         <v>85723</v>
@@ -17521,10 +17517,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>695341</v>
+        <v>695320</v>
       </c>
       <c r="R155" t="n">
-        <v>6362752</v>
+        <v>6362559</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17587,10 +17583,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>112772355</v>
+        <v>112772288</v>
       </c>
       <c r="B156" t="n">
-        <v>85723</v>
+        <v>85587</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17603,21 +17599,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17627,10 +17623,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>695320</v>
+        <v>695282</v>
       </c>
       <c r="R156" t="n">
-        <v>6362559</v>
+        <v>6362753</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17693,10 +17689,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>112772288</v>
+        <v>112772351</v>
       </c>
       <c r="B157" t="n">
-        <v>85587</v>
+        <v>85723</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17709,21 +17705,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17736,7 +17732,7 @@
         <v>695282</v>
       </c>
       <c r="R157" t="n">
-        <v>6362753</v>
+        <v>6362751</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17799,37 +17795,37 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>112772351</v>
+        <v>112772291</v>
       </c>
       <c r="B158" t="n">
-        <v>85723</v>
+        <v>86215</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17839,10 +17835,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>695282</v>
+        <v>695280</v>
       </c>
       <c r="R158" t="n">
-        <v>6362751</v>
+        <v>6362752</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17905,37 +17901,37 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>112772291</v>
+        <v>112772289</v>
       </c>
       <c r="B159" t="n">
-        <v>86215</v>
+        <v>85587</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17945,10 +17941,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>695280</v>
+        <v>695313</v>
       </c>
       <c r="R159" t="n">
-        <v>6362752</v>
+        <v>6362617</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18011,10 +18007,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>112772289</v>
+        <v>112772294</v>
       </c>
       <c r="B160" t="n">
-        <v>85587</v>
+        <v>88493</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18027,21 +18023,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>3712</v>
+        <v>245042</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18051,10 +18047,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>695313</v>
+        <v>695269</v>
       </c>
       <c r="R160" t="n">
-        <v>6362617</v>
+        <v>6362751</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18117,37 +18113,37 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>112772294</v>
+        <v>112772287</v>
       </c>
       <c r="B161" t="n">
-        <v>88493</v>
+        <v>90110</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>245042</v>
+        <v>2015</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -18157,10 +18153,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>695269</v>
+        <v>695278</v>
       </c>
       <c r="R161" t="n">
-        <v>6362751</v>
+        <v>6362757</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18223,37 +18219,37 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>112772287</v>
+        <v>112772352</v>
       </c>
       <c r="B162" t="n">
-        <v>90110</v>
+        <v>85723</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>2015</v>
+        <v>3674</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -18263,10 +18259,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>695278</v>
+        <v>695269</v>
       </c>
       <c r="R162" t="n">
-        <v>6362757</v>
+        <v>6362716</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18329,7 +18325,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>112772352</v>
+        <v>112772345</v>
       </c>
       <c r="B163" t="n">
         <v>85723</v>
@@ -18369,10 +18365,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>695269</v>
+        <v>695340</v>
       </c>
       <c r="R163" t="n">
-        <v>6362716</v>
+        <v>6362774</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18435,7 +18431,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>112772345</v>
+        <v>112772354</v>
       </c>
       <c r="B164" t="n">
         <v>85723</v>
@@ -18475,10 +18471,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>695340</v>
+        <v>695259</v>
       </c>
       <c r="R164" t="n">
-        <v>6362774</v>
+        <v>6362641</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18541,7 +18537,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>112772354</v>
+        <v>112772357</v>
       </c>
       <c r="B165" t="n">
         <v>85723</v>
@@ -18581,10 +18577,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>695259</v>
+        <v>695353</v>
       </c>
       <c r="R165" t="n">
-        <v>6362641</v>
+        <v>6362526</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18647,10 +18643,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>112772357</v>
+        <v>112791840</v>
       </c>
       <c r="B166" t="n">
-        <v>85723</v>
+        <v>85760</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18683,14 +18679,14 @@
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Klinte skjutbana, Gtl</t>
+          <t>Mulde-Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>695353</v>
+        <v>695372</v>
       </c>
       <c r="R166" t="n">
-        <v>6362526</v>
+        <v>6362556</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18737,12 +18733,12 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -18753,10 +18749,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>112791840</v>
+        <v>112791835</v>
       </c>
       <c r="B167" t="n">
-        <v>85760</v>
+        <v>85624</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18769,21 +18765,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18793,10 +18789,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>695372</v>
+        <v>695405</v>
       </c>
       <c r="R167" t="n">
-        <v>6362556</v>
+        <v>6362565</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18859,10 +18855,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>112791835</v>
+        <v>112791839</v>
       </c>
       <c r="B168" t="n">
-        <v>85624</v>
+        <v>85760</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18875,21 +18871,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18899,10 +18895,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>695405</v>
+        <v>695324</v>
       </c>
       <c r="R168" t="n">
-        <v>6362565</v>
+        <v>6362693</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18965,7 +18961,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>112791839</v>
+        <v>112791838</v>
       </c>
       <c r="B169" t="n">
         <v>85760</v>
@@ -19005,10 +19001,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>695324</v>
+        <v>695257</v>
       </c>
       <c r="R169" t="n">
-        <v>6362693</v>
+        <v>6362646</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19071,10 +19067,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>112791838</v>
+        <v>112791834</v>
       </c>
       <c r="B170" t="n">
-        <v>85760</v>
+        <v>85624</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19087,21 +19083,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19111,10 +19107,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>695257</v>
+        <v>695346</v>
       </c>
       <c r="R170" t="n">
-        <v>6362646</v>
+        <v>6362670</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19177,10 +19173,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>112791834</v>
+        <v>112791836</v>
       </c>
       <c r="B171" t="n">
-        <v>85624</v>
+        <v>105393</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19189,25 +19185,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>3712</v>
+        <v>221849</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19217,10 +19213,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>695346</v>
+        <v>695366</v>
       </c>
       <c r="R171" t="n">
-        <v>6362670</v>
+        <v>6362488</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19283,14 +19279,14 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>112791836</v>
+        <v>112831273</v>
       </c>
       <c r="B172" t="n">
-        <v>105393</v>
+        <v>86661</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -19299,37 +19295,40 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>221849</v>
+        <v>510</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Mulde-Ansarve, Gtl</t>
+          <t>Lilla Snögrinde, Gtl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>695366</v>
+        <v>695314</v>
       </c>
       <c r="R172" t="n">
-        <v>6362488</v>
+        <v>6362616</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -19367,75 +19366,70 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY172" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, Gotland</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>112831273</v>
+        <v>112716741</v>
       </c>
       <c r="B173" t="n">
-        <v>86661</v>
+        <v>85766</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>510</v>
+        <v>3674</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Lilla Snögrinde, Gtl</t>
+          <t>Utskogen, Gtl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>695314</v>
+        <v>695320</v>
       </c>
       <c r="R173" t="n">
-        <v>6362616</v>
+        <v>6362625</v>
       </c>
       <c r="S173" t="n">
         <v>25</v>
@@ -19476,7 +19470,6 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -19495,10 +19488,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>112716741</v>
+        <v>112716830</v>
       </c>
       <c r="B174" t="n">
-        <v>85766</v>
+        <v>8427</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19511,21 +19504,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>3674</v>
+        <v>106545</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19536,10 +19529,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>695320</v>
+        <v>695318</v>
       </c>
       <c r="R174" t="n">
-        <v>6362625</v>
+        <v>6362680</v>
       </c>
       <c r="S174" t="n">
         <v>25</v>
@@ -19598,10 +19591,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>112716830</v>
+        <v>113014673</v>
       </c>
       <c r="B175" t="n">
-        <v>8427</v>
+        <v>85731</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19614,38 +19607,37 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>106545</v>
+        <v>3712</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Utskogen, Gtl</t>
+          <t>Klinte skjutbana, ca 2,5 km N Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>695318</v>
+        <v>695296</v>
       </c>
       <c r="R175" t="n">
-        <v>6362680</v>
+        <v>6362619</v>
       </c>
       <c r="S175" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -19689,22 +19681,26 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michael Krikorev</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY175" t="inlineStr"/>
+          <t>Michael Krikorev</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>113014673</v>
+        <v>113014688</v>
       </c>
       <c r="B176" t="n">
-        <v>85731</v>
+        <v>85867</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19717,21 +19713,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19741,10 +19737,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>695296</v>
+        <v>695295</v>
       </c>
       <c r="R176" t="n">
-        <v>6362619</v>
+        <v>6362537</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19807,37 +19803,37 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>113014688</v>
+        <v>113014672</v>
       </c>
       <c r="B177" t="n">
-        <v>85867</v>
+        <v>90110</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>3674</v>
+        <v>2015</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19847,10 +19843,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>695295</v>
+        <v>695331</v>
       </c>
       <c r="R177" t="n">
-        <v>6362537</v>
+        <v>6362709</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19913,37 +19909,37 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>113014672</v>
+        <v>113014690</v>
       </c>
       <c r="B178" t="n">
-        <v>90110</v>
+        <v>85867</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>2015</v>
+        <v>3674</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19953,10 +19949,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>695331</v>
+        <v>695338</v>
       </c>
       <c r="R178" t="n">
-        <v>6362709</v>
+        <v>6362669</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20019,10 +20015,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>113014690</v>
+        <v>113014677</v>
       </c>
       <c r="B179" t="n">
-        <v>85867</v>
+        <v>85731</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20035,21 +20031,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -20059,10 +20055,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>695338</v>
+        <v>695331</v>
       </c>
       <c r="R179" t="n">
-        <v>6362669</v>
+        <v>6362665</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20125,37 +20121,37 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>113014677</v>
+        <v>113014682</v>
       </c>
       <c r="B180" t="n">
-        <v>85731</v>
+        <v>86215</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Belägg granskat av validerare.</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20165,10 +20161,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>695331</v>
+        <v>695347</v>
       </c>
       <c r="R180" t="n">
-        <v>6362665</v>
+        <v>6362767</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20231,10 +20227,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>113014682</v>
+        <v>113014686</v>
       </c>
       <c r="B181" t="n">
-        <v>86215</v>
+        <v>86068</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20243,25 +20239,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20271,10 +20267,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>695347</v>
+        <v>695348</v>
       </c>
       <c r="R181" t="n">
-        <v>6362767</v>
+        <v>6362751</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20337,37 +20333,37 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>113014686</v>
+        <v>113014675</v>
       </c>
       <c r="B182" t="n">
-        <v>86068</v>
+        <v>85731</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -20377,10 +20373,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>695348</v>
+        <v>695325</v>
       </c>
       <c r="R182" t="n">
-        <v>6362751</v>
+        <v>6362726</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20443,7 +20439,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>113014675</v>
+        <v>113014678</v>
       </c>
       <c r="B183" t="n">
         <v>85731</v>
@@ -20483,10 +20479,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>695325</v>
+        <v>695346</v>
       </c>
       <c r="R183" t="n">
-        <v>6362726</v>
+        <v>6362663</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20549,7 +20545,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>113014678</v>
+        <v>113014676</v>
       </c>
       <c r="B184" t="n">
         <v>85731</v>
@@ -20589,10 +20585,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>695346</v>
+        <v>695324</v>
       </c>
       <c r="R184" t="n">
-        <v>6362663</v>
+        <v>6362692</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20655,10 +20651,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>113014676</v>
+        <v>113014683</v>
       </c>
       <c r="B185" t="n">
-        <v>85731</v>
+        <v>85904</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20667,25 +20663,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20695,10 +20691,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>695324</v>
+        <v>695326</v>
       </c>
       <c r="R185" t="n">
-        <v>6362692</v>
+        <v>6362713</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20761,7 +20757,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>113014683</v>
+        <v>113014684</v>
       </c>
       <c r="B186" t="n">
         <v>85904</v>
@@ -20801,10 +20797,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>695326</v>
+        <v>695324</v>
       </c>
       <c r="R186" t="n">
-        <v>6362713</v>
+        <v>6362665</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20867,10 +20863,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>113014684</v>
+        <v>113014689</v>
       </c>
       <c r="B187" t="n">
-        <v>85904</v>
+        <v>85867</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20879,25 +20875,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20907,10 +20903,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>695324</v>
+        <v>695336</v>
       </c>
       <c r="R187" t="n">
-        <v>6362665</v>
+        <v>6362743</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20973,10 +20969,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>113014689</v>
+        <v>113014674</v>
       </c>
       <c r="B188" t="n">
-        <v>85867</v>
+        <v>85731</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20989,21 +20985,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -21013,10 +21009,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>695336</v>
+        <v>695341</v>
       </c>
       <c r="R188" t="n">
-        <v>6362743</v>
+        <v>6362751</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21079,7 +21075,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>113014674</v>
+        <v>113014679</v>
       </c>
       <c r="B189" t="n">
         <v>85731</v>
@@ -21119,10 +21115,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>695341</v>
+        <v>695365</v>
       </c>
       <c r="R189" t="n">
-        <v>6362751</v>
+        <v>6362626</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21185,7 +21181,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>113014679</v>
+        <v>113014681</v>
       </c>
       <c r="B190" t="n">
         <v>85731</v>
@@ -21225,10 +21221,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>695365</v>
+        <v>695360</v>
       </c>
       <c r="R190" t="n">
-        <v>6362626</v>
+        <v>6362563</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21291,10 +21287,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>113014681</v>
+        <v>113014692</v>
       </c>
       <c r="B191" t="n">
-        <v>85731</v>
+        <v>85867</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -21307,21 +21303,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -21331,10 +21327,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>695360</v>
+        <v>695366</v>
       </c>
       <c r="R191" t="n">
-        <v>6362563</v>
+        <v>6362645</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21397,10 +21393,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>113014692</v>
+        <v>114549083</v>
       </c>
       <c r="B192" t="n">
-        <v>85867</v>
+        <v>103157</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -21409,41 +21405,41 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>3674</v>
+        <v>220164</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Klinte skjutbana, ca 2,5 km N Ansarve, Gtl</t>
+          <t>Klinte Prästgården 1:1 (1), Gtl</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>695366</v>
+        <v>695291</v>
       </c>
       <c r="R192" t="n">
-        <v>6362645</v>
+        <v>6362535</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21483,30 +21479,31 @@
       </c>
       <c r="AG192" t="b">
         <v>0</v>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gläntor.</t>
+        </is>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Michael Krikorev</t>
-        </is>
-      </c>
-      <c r="AY192" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, Gotland</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>114549083</v>
+        <v>114549082</v>
       </c>
       <c r="B193" t="n">
-        <v>103157</v>
+        <v>105917</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21519,21 +21516,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21543,10 +21540,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>695291</v>
+        <v>695326</v>
       </c>
       <c r="R193" t="n">
-        <v>6362535</v>
+        <v>6362494</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -21610,7 +21607,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>114549082</v>
+        <v>114549084</v>
       </c>
       <c r="B194" t="n">
         <v>105917</v>
@@ -21650,10 +21647,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>695326</v>
+        <v>695291</v>
       </c>
       <c r="R194" t="n">
-        <v>6362494</v>
+        <v>6362535</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -21717,7 +21714,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>114549084</v>
+        <v>114549087</v>
       </c>
       <c r="B195" t="n">
         <v>105917</v>
@@ -21757,10 +21754,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>695291</v>
+        <v>695341</v>
       </c>
       <c r="R195" t="n">
-        <v>6362535</v>
+        <v>6362527</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -21824,10 +21821,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>114549087</v>
+        <v>114549086</v>
       </c>
       <c r="B196" t="n">
-        <v>105917</v>
+        <v>100812</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -21836,25 +21833,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>221849</v>
+        <v>221235</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -21864,10 +21861,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>695341</v>
+        <v>695332</v>
       </c>
       <c r="R196" t="n">
-        <v>6362527</v>
+        <v>6362548</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -21928,113 +21925,6 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>114549086</v>
-      </c>
-      <c r="B197" t="n">
-        <v>100812</v>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E197" t="n">
-        <v>221235</v>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>Vårärt</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>Lathyrus vernus</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="P197" t="inlineStr">
-        <is>
-          <t>Klinte Prästgården 1:1 (1), Gtl</t>
-        </is>
-      </c>
-      <c r="Q197" t="n">
-        <v>695332</v>
-      </c>
-      <c r="R197" t="n">
-        <v>6362548</v>
-      </c>
-      <c r="S197" t="n">
-        <v>5</v>
-      </c>
-      <c r="T197" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="U197" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="V197" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="W197" t="inlineStr">
-        <is>
-          <t>Fröjel</t>
-        </is>
-      </c>
-      <c r="Y197" t="inlineStr">
-        <is>
-          <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AA197" t="inlineStr">
-        <is>
-          <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AD197" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE197" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG197" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI197" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, gläntor.</t>
-        </is>
-      </c>
-      <c r="AT197" t="inlineStr"/>
-      <c r="AW197" t="inlineStr">
-        <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AX197" t="inlineStr">
-        <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY197" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9921-2023 artfynd.xlsx
+++ b/artfynd/A 9921-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY216"/>
+  <dimension ref="A1:AZ216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16869376</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104129758</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104130308</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104130433</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,6 +1215,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104130614</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104130642</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1393,6 +1428,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142313</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142526</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1599,6 +1644,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179900</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282753</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1801,6 +1856,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282754</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1902,6 +1962,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282755</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2003,6 +2068,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282756</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2104,6 +2174,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113014686</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2198,6 +2273,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104130176</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16869377</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2402,6 +2487,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104130706</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2503,6 +2593,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112730615</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2602,6 +2697,11 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179905</t>
         </is>
       </c>
     </row>
@@ -2705,6 +2805,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112831273</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2806,6 +2911,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729827</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2912,6 +3022,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16869378</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3009,6 +3124,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662080</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3106,6 +3226,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662081</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3203,6 +3328,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662082</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3300,6 +3430,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662083</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3397,6 +3532,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662085</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3494,6 +3634,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662086</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3591,6 +3736,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662087</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3688,6 +3838,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662088</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3785,6 +3940,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662102</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3882,6 +4042,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662103</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3979,6 +4144,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662104</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4076,6 +4246,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662105</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4173,6 +4348,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662106</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4270,6 +4450,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662109</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4368,6 +4553,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104130201</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4476,6 +4666,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104130424</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4581,6 +4776,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142302</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4680,6 +4880,11 @@
       <c r="AY41" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282713</t>
         </is>
       </c>
     </row>
@@ -4787,6 +4992,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112723884</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4888,6 +5098,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772287</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4987,6 +5202,11 @@
       <c r="AY44" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113014672</t>
         </is>
       </c>
     </row>
@@ -5094,6 +5314,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142519</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5191,6 +5416,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662125</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5292,6 +5522,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179904</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5393,6 +5628,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729812</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5490,6 +5730,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662099</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5587,6 +5832,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662136</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5695,6 +5945,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104129865</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5793,6 +6048,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104130159</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5898,6 +6158,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142318</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6003,6 +6268,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142319</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6108,6 +6378,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142320</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6213,6 +6488,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142527</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6314,6 +6594,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282764</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6412,6 +6697,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112716645</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6510,6 +6800,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112716741</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6615,6 +6910,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112716742</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6720,6 +7020,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112723769</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6825,6 +7130,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112723784</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6930,6 +7240,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112723839</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7035,6 +7350,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112723847</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7140,6 +7460,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112723853</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7245,6 +7570,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112723874</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7350,6 +7680,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112723909</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7455,6 +7790,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112723941</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7560,6 +7900,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725265</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7665,6 +8010,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725267</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7770,6 +8120,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725488</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7871,6 +8226,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729698</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7972,6 +8332,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729699</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8073,6 +8438,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729700</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8174,6 +8544,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729814</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8275,6 +8650,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729816</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8376,6 +8756,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729830</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8477,6 +8862,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729831</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8578,6 +8968,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729832</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8679,6 +9074,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112730612</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8780,6 +9180,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112730613</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8881,6 +9286,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112730614</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8982,6 +9392,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772345</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9083,6 +9498,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772348</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9184,6 +9604,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772349</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9285,6 +9710,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772351</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9386,6 +9816,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772352</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9487,6 +9922,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772354</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9588,6 +10028,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772355</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9689,6 +10134,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772357</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9790,6 +10240,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791838</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9891,6 +10346,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791839</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9992,6 +10452,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791840</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10093,6 +10558,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113014688</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10194,6 +10664,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113014689</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10295,6 +10770,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113014690</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10396,6 +10876,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113014692</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10493,6 +10978,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662130</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10590,6 +11080,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662131</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10687,6 +11182,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662132</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10795,6 +11295,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104129779</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10893,6 +11398,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104130161</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10998,6 +11508,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142314</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11103,6 +11618,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142522</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11204,6 +11724,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179907</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11305,6 +11830,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179908</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11406,6 +11936,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179909</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11507,6 +12042,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282731</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11608,6 +12148,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282732</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11706,6 +12251,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112716773</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11811,6 +12361,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112723931</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11916,6 +12471,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725259</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12017,6 +12577,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729697</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12118,6 +12683,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729806</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12219,6 +12789,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112730606</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12320,6 +12895,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112730607</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12421,6 +13001,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112730608</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12522,6 +13107,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772288</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12623,6 +13213,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772289</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12724,6 +13319,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791834</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12825,6 +13425,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791835</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12926,6 +13531,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113014673</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13027,6 +13637,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113014674</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13128,6 +13743,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113014675</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13229,6 +13849,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113014676</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13330,6 +13955,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113014677</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13431,6 +14061,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113014678</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13532,6 +14167,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113014679</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13631,6 +14271,11 @@
       <c r="AY129" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113014681</t>
         </is>
       </c>
     </row>
@@ -13738,6 +14383,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142520</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13839,6 +14489,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179901</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13936,6 +14591,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662127</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14037,6 +14697,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112730605</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14134,6 +14799,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662124</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14239,6 +14909,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142307</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14340,6 +15015,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282725</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14441,6 +15121,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729696</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14540,6 +15225,11 @@
       <c r="AY138" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729828</t>
         </is>
       </c>
     </row>
@@ -14647,6 +15337,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142308</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14744,6 +15439,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662126</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14841,6 +15541,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662120</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14938,6 +15643,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662110</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15036,6 +15746,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109534905</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15133,6 +15848,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662100</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15230,6 +15950,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662101</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15331,6 +16056,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179898</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15428,6 +16158,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662119</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15531,6 +16266,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109534717</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15629,6 +16369,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112716830</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15727,6 +16472,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109534692</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15825,6 +16575,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109534436</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15923,6 +16678,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109534773</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16021,6 +16781,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109534913</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16118,6 +16883,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662121</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16219,6 +16989,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791832</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16321,6 +17096,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114549079</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16423,6 +17203,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114549083</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16521,6 +17306,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109534766</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16623,6 +17413,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114549086</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16720,6 +17515,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69261619</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16817,6 +17617,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662135</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16918,6 +17723,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791836</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17019,6 +17829,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791837</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17121,6 +17936,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114549080</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17223,6 +18043,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114549081</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17325,6 +18150,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114549082</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17427,6 +18257,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114549084</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17529,6 +18364,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114549087</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17631,6 +18471,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114549078</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17729,6 +18574,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109534776</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17827,6 +18677,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109534927</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17924,6 +18779,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662094</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18032,6 +18892,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104130367</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18130,6 +18995,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104130267</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18231,6 +19101,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772294</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18328,6 +19203,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662129</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18426,6 +19306,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104130138</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18531,6 +19416,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142523</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18636,6 +19526,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725263</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18734,6 +19629,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104130183</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18839,6 +19739,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142309</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18944,6 +19849,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142310</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19049,6 +19959,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142525</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19150,6 +20065,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179902</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19251,6 +20171,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179903</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19352,6 +20277,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282744</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19453,6 +20383,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282745</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19554,6 +20489,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282746</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19652,6 +20592,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662111</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19750,6 +20695,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104130197</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19848,6 +20798,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104130263</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19953,6 +20908,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142303</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20058,6 +21018,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142304</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20159,6 +21124,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282721</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20258,6 +21228,11 @@
       <c r="AY195" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282722</t>
         </is>
       </c>
     </row>
@@ -20365,6 +21340,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725260</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20470,6 +21450,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112725262</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20571,6 +21556,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729690</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20672,6 +21662,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729691</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20773,6 +21768,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729692</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20874,6 +21874,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729693</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20975,6 +21980,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729807</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -21076,6 +22086,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729810</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -21177,6 +22192,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729826</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -21278,6 +22298,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112730609</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21379,6 +22404,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112730610</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21480,6 +22510,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112730611</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21581,6 +22616,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772290</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21682,6 +22722,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112772291</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21783,6 +22828,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113014682</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21884,6 +22934,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113014683</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21985,6 +23040,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113014684</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -22082,6 +23142,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662128</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -22183,6 +23248,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282734</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -22280,6 +23350,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104179897</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -22377,8 +23452,230 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729825</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>